--- a/templates/이뮨.xlsx
+++ b/templates/이뮨.xlsx
@@ -2,46 +2,45 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="525" windowWidth="27735" windowHeight="11250" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이뮨" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,21 +53,17 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -141,7 +136,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -215,7 +210,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -250,7 +244,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -429,208 +422,95 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr autoPageBreaks="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="2" min="1" max="38"/>
+    <col width="19.75" customWidth="1" min="1" max="1"/>
+    <col width="24.5" customWidth="1" min="2" max="2"/>
+    <col width="12.625" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="65.375" customWidth="1" min="10" max="10"/>
+    <col width="12.625" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="2">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>오더코드</t>
+          <t>상품고유코드</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>릴리즈코드</t>
+          <t>판매상품명</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>택배사</t>
+          <t>수량</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>송장번호</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>고유코드</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>판매상품명</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>배송방식</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>주문자 이름</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>받는분 이름</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>전화번호1</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>전화번호2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>우편번호</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>배송메시지</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>주문번호</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>관리메모1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>관리메모2</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>관리메모3</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>관리메모4</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>관리메모5</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>상품별 메모1</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>상품별 메모2</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>상품별 메모3</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>정보1</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>정보2</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>정보3</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>정보4</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>정보5</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>정보6</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>발주 타입</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>공급사명</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>출고희망일</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>발주일자</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>신용번호(계약코드)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>택배구분</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>진행상태</t>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>주소1</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>합배송</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>배송 특이사항</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>관리번호</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" firstPageNumber="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>